--- a/data/availability/projects/arabella-group/direction-white.xlsx
+++ b/data/availability/projects/arabella-group/direction-white.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for direction-white</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -554,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ranch Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -987,7 +997,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Jun 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1047,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Jun 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1097,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Jun 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1147,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Jun 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1204,7 +1214,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ranch Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1435,7 +1445,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ranch Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1474,7 +1484,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1535,7 +1545,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1764,7 +1774,6 @@
       <c r="G7" t="n">
         <v>65</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1821,7 +1830,6 @@
       <c r="G8" t="n">
         <v>105</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1878,7 +1886,6 @@
       <c r="G9" t="n">
         <v>120</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1935,7 +1942,6 @@
       <c r="G10" t="n">
         <v>155</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -2007,7 +2013,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Jun 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2068,7 +2074,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Jun 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2114,7 +2120,6 @@
       <c r="G13" t="n">
         <v>65</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -2125,7 +2130,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Jun 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2171,7 +2176,6 @@
       <c r="G14" t="n">
         <v>145</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -2182,7 +2186,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Jun 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2265,7 +2269,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ranch Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2350,7 +2354,6 @@
       <c r="G17" t="n">
         <v>65</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -2407,7 +2410,6 @@
       <c r="G18" t="n">
         <v>125</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
